--- a/Results/Generator_GPT-4o_Analyser_Llama3-2.xlsx
+++ b/Results/Generator_GPT-4o_Analyser_Llama3-2.xlsx
@@ -27,7 +27,6 @@
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <family val="3"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
@@ -74,10 +73,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -500,14 +502,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>WILLIAM HOGARTH</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>William Turner</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -517,22 +519,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -542,24 +544,24 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>EDGAR DEGAS</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Jacob Jordaens</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,7 +571,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -584,7 +586,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -594,17 +596,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -614,9 +616,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>PAUL GAUGUIN</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Hans Holbein the Younger</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -626,12 +628,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -641,17 +643,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -666,14 +668,14 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>JOSEPH-MALLORD WILLIAM TURNER</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Paul Gauguin</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -683,7 +685,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -701,9 +703,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-1</t>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -713,7 +715,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -728,9 +730,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MICHELANGELO BUONARROTI</t>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Michelangelo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -740,12 +742,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -755,7 +757,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -770,7 +772,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -785,9 +787,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ANDY WARHOL</t>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Edgar Degas</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -797,94 +799,94 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CASPAR DAVID FRIEDRICH</t>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Andy Warhol</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -899,9 +901,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HANS HOLBEIN THE YOUNGER</t>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Vasily Vereshchagin</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -926,12 +928,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -956,24 +958,24 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>JEAN-ANTOINE WATTEAU</t>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Camille Corot</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -983,17 +985,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1008,14 +1010,14 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>JEAN-BAPTISTE CAMILLE COROT</t>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Salvador Dali</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1030,7 +1032,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1040,27 +1042,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
